--- a/data/trans_bre/P16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,18</t>
+          <t>2,18; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,55</t>
+          <t>2,8; 6,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,29</t>
+          <t>2,67; 6,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,13</t>
+          <t>0,2; 3,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,29; 517,01</t>
+          <t>72,76; 491,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>186,97; 1626,7</t>
+          <t>177,81; 1613,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>171,55; 1874,55</t>
+          <t>184,82; 1868,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 162,58</t>
+          <t>2,19; 194,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,94</t>
+          <t>1,19; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,2</t>
+          <t>3,72; 7,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,27</t>
+          <t>0,62; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,67</t>
+          <t>2,01; 4,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,22; 301,36</t>
+          <t>32,53; 311,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>188,25; 980,42</t>
+          <t>193,73; 983,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,68; 446,67</t>
+          <t>28,44; 454,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>109,12; 665,32</t>
+          <t>100,42; 625,24</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,7</t>
+          <t>1,69; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,51</t>
+          <t>2,28; 6,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,96</t>
+          <t>0,75; 4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,95</t>
+          <t>-1,34; 2,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,58; 586,03</t>
+          <t>52,0; 614,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,72; 735,11</t>
+          <t>63,64; 774,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 448,82</t>
+          <t>22,98; 439,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 170,68</t>
+          <t>-39,95; 163,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,55</t>
+          <t>0,57; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,13</t>
+          <t>2,5; 6,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,86</t>
+          <t>1,84; 4,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,59</t>
+          <t>2,92; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 185,55</t>
+          <t>15,61; 189,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>101,88; 502,31</t>
+          <t>98,58; 568,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,97; 484,17</t>
+          <t>76,86; 481,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,82; 448,18</t>
+          <t>94,65; 442,78</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,99</t>
+          <t>2,15; 4,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,62</t>
+          <t>3,78; 5,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,65</t>
+          <t>2,0; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,78</t>
+          <t>1,98; 3,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,59; 222,67</t>
+          <t>79,37; 217,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>221,47; 535,8</t>
+          <t>216,49; 535,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>130,28; 361,75</t>
+          <t>127,53; 354,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,72; 237,71</t>
+          <t>87,24; 239,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,32</t>
+          <t>1,96; 6,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,51</t>
+          <t>2,69; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,3</t>
+          <t>2,69; 6,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,43</t>
+          <t>0,09; 3,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,76; 491,81</t>
+          <t>65,01; 538,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>177,81; 1613,3</t>
+          <t>168,23; 1434,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>184,82; 1868,35</t>
+          <t>170,45; 2185,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 194,79</t>
+          <t>-0,73; 156,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>245,84%</t>
+          <t>181,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,02</t>
+          <t>1,18; 5,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,27</t>
+          <t>3,64; 7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,41</t>
+          <t>0,66; 3,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,65</t>
+          <t>1,7; 4,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,53; 311,87</t>
+          <t>31,79; 307,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>193,73; 983,02</t>
+          <t>185,7; 1002,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 454,95</t>
+          <t>29,51; 430,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>100,42; 625,24</t>
+          <t>70,61; 383,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,84</t>
+          <t>1,59; 5,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,65</t>
+          <t>2,25; 6,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,08</t>
+          <t>0,88; 4,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,83</t>
+          <t>0,47; 4,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,0; 614,58</t>
+          <t>36,38; 609,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,64; 774,13</t>
+          <t>62,09; 810,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,98; 439,79</t>
+          <t>25,64; 402,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 163,18</t>
+          <t>8,25; 211,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>225,91%</t>
+          <t>257,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,86</t>
+          <t>0,59; 3,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,16</t>
+          <t>2,37; 5,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,83</t>
+          <t>1,64; 4,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,56</t>
+          <t>3,58; 6,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 189,47</t>
+          <t>15,06; 182,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,58; 568,14</t>
+          <t>96,8; 531,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,86; 481,92</t>
+          <t>71,18; 471,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,65; 442,78</t>
+          <t>116,26; 498,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148,7%</t>
+          <t>145,79%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,06</t>
+          <t>2,09; 4,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,63</t>
+          <t>3,78; 5,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,69</t>
+          <t>2,09; 3,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,88</t>
+          <t>2,42; 3,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,37; 217,92</t>
+          <t>78,61; 215,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>216,49; 535,91</t>
+          <t>219,64; 572,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>127,53; 354,21</t>
+          <t>129,27; 367,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,24; 239,65</t>
+          <t>92,95; 213,25</t>
         </is>
       </c>
     </row>
